--- a/site/leagues/proliga/2026_2027/xlsx/team_packs/team_pack_MBC.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/team_packs/team_pack_MBC.xlsx
@@ -963,7 +963,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D5" t="n">
